--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/40.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/40.xlsx
@@ -426,13 +426,13 @@
         <v>-15.34333561291029</v>
       </c>
       <c r="E2">
-        <v>-23.80592275506422</v>
+        <v>-26.79406349986955</v>
       </c>
       <c r="F2">
-        <v>-2.690396294913074</v>
+        <v>-3.243887259005922</v>
       </c>
       <c r="G2">
-        <v>-17.57200940256494</v>
+        <v>-22.05381933253919</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.00580617803643</v>
       </c>
       <c r="E3">
-        <v>-25.49995695422358</v>
+        <v>-27.24704675485681</v>
       </c>
       <c r="F3">
-        <v>-2.251193468207914</v>
+        <v>-3.896664706202457</v>
       </c>
       <c r="G3">
-        <v>-18.38010363706442</v>
+        <v>-22.27151087556505</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.6483446026432</v>
       </c>
       <c r="E4">
-        <v>-26.09068280310216</v>
+        <v>-27.88248222761312</v>
       </c>
       <c r="F4">
-        <v>-2.481329693309997</v>
+        <v>-3.608150705498403</v>
       </c>
       <c r="G4">
-        <v>-17.18904383930927</v>
+        <v>-20.90651832572214</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.29372191834154</v>
       </c>
       <c r="E5">
-        <v>-25.69543759171269</v>
+        <v>-28.10972558179203</v>
       </c>
       <c r="F5">
-        <v>-2.325856491738349</v>
+        <v>-3.462330983334316</v>
       </c>
       <c r="G5">
-        <v>-17.34024969626995</v>
+        <v>-21.18896745004168</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.92098722387481</v>
       </c>
       <c r="E6">
-        <v>-26.1355146957781</v>
+        <v>-29.92873434237807</v>
       </c>
       <c r="F6">
-        <v>-2.260684617759142</v>
+        <v>-3.141084156917001</v>
       </c>
       <c r="G6">
-        <v>-16.91958032986753</v>
+        <v>-22.97169622293921</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.53535233883662</v>
       </c>
       <c r="E7">
-        <v>-27.02533266744128</v>
+        <v>-29.55850215716997</v>
       </c>
       <c r="F7">
-        <v>-2.270753819969507</v>
+        <v>-3.06246107674501</v>
       </c>
       <c r="G7">
-        <v>-17.03614298303249</v>
+        <v>-21.10191003399546</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.12943944047911</v>
       </c>
       <c r="E8">
-        <v>-26.78109395031158</v>
+        <v>-30.70568689211108</v>
       </c>
       <c r="F8">
-        <v>-2.303849314337402</v>
+        <v>-2.517685246304825</v>
       </c>
       <c r="G8">
-        <v>-17.20121174943887</v>
+        <v>-20.82194547410315</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.6814726595808</v>
       </c>
       <c r="E9">
-        <v>-27.29150278419011</v>
+        <v>-31.32528629126256</v>
       </c>
       <c r="F9">
-        <v>-2.156338194255626</v>
+        <v>-2.389560270333943</v>
       </c>
       <c r="G9">
-        <v>-16.20525067667683</v>
+        <v>-20.46368320166153</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.17584865423869</v>
       </c>
       <c r="E10">
-        <v>-28.09057466521359</v>
+        <v>-31.43909137154933</v>
       </c>
       <c r="F10">
-        <v>-2.311403591554048</v>
+        <v>-3.02770348301886</v>
       </c>
       <c r="G10">
-        <v>-15.78746479543911</v>
+        <v>-21.06595916471175</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.61308631334432</v>
       </c>
       <c r="E11">
-        <v>-29.17247239038612</v>
+        <v>-33.14150324762289</v>
       </c>
       <c r="F11">
-        <v>-1.960804359699979</v>
+        <v>-2.883223576059235</v>
       </c>
       <c r="G11">
-        <v>-15.56175014529883</v>
+        <v>-21.03096504308888</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.98470328412272</v>
       </c>
       <c r="E12">
-        <v>-29.43691715853803</v>
+        <v>-31.71057791678317</v>
       </c>
       <c r="F12">
-        <v>-1.940506792834749</v>
+        <v>-2.521905822569471</v>
       </c>
       <c r="G12">
-        <v>-16.08111515059078</v>
+        <v>-20.65849225391994</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.28436855666762</v>
       </c>
       <c r="E13">
-        <v>-29.64874558719483</v>
+        <v>-34.18330586393149</v>
       </c>
       <c r="F13">
-        <v>-1.990101335429693</v>
+        <v>-2.091385663545708</v>
       </c>
       <c r="G13">
-        <v>-14.97939539003118</v>
+        <v>-19.78819948982864</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.536040385944702</v>
       </c>
       <c r="E14">
-        <v>-29.76438017098069</v>
+        <v>-32.99463804284312</v>
       </c>
       <c r="F14">
-        <v>-1.765896088980931</v>
+        <v>-2.816247861042343</v>
       </c>
       <c r="G14">
-        <v>-14.94325416437895</v>
+        <v>-19.36024361269428</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.75074343648747</v>
       </c>
       <c r="E15">
-        <v>-30.61315884694936</v>
+        <v>-36.68014793517066</v>
       </c>
       <c r="F15">
-        <v>-1.586110626048414</v>
+        <v>-2.027000099553517</v>
       </c>
       <c r="G15">
-        <v>-14.55015998704589</v>
+        <v>-18.6976081280993</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.934732083559788</v>
       </c>
       <c r="E16">
-        <v>-31.8760211861794</v>
+        <v>-35.57149598556082</v>
       </c>
       <c r="F16">
-        <v>-1.671644206982425</v>
+        <v>-1.296953640742691</v>
       </c>
       <c r="G16">
-        <v>-14.10649722660046</v>
+        <v>-19.97559623062462</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.111698735060259</v>
       </c>
       <c r="E17">
-        <v>-32.5125751920156</v>
+        <v>-37.0408340971706</v>
       </c>
       <c r="F17">
-        <v>-1.654614617273705</v>
+        <v>-1.867732338608476</v>
       </c>
       <c r="G17">
-        <v>-13.22812011030226</v>
+        <v>-18.17171472700391</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.295647567574186</v>
       </c>
       <c r="E18">
-        <v>-33.77237401857946</v>
+        <v>-35.35202575701608</v>
       </c>
       <c r="F18">
-        <v>-1.284589648660855</v>
+        <v>-1.782601810829944</v>
       </c>
       <c r="G18">
-        <v>-12.5326605666854</v>
+        <v>-18.16385714716645</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.491971760816235</v>
       </c>
       <c r="E19">
-        <v>-34.07571837845726</v>
+        <v>-37.46932510048737</v>
       </c>
       <c r="F19">
-        <v>-1.399313305175289</v>
+        <v>-1.440645654009385</v>
       </c>
       <c r="G19">
-        <v>-12.97532685292351</v>
+        <v>-19.26080475633119</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.714779192970309</v>
       </c>
       <c r="E20">
-        <v>-34.37416519369577</v>
+        <v>-38.41388326595527</v>
       </c>
       <c r="F20">
-        <v>-1.239572016161531</v>
+        <v>-0.7142401350981543</v>
       </c>
       <c r="G20">
-        <v>-13.08008244542267</v>
+        <v>-18.33440155589478</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.978088859251775</v>
       </c>
       <c r="E21">
-        <v>-34.87796471976012</v>
+        <v>-40.62365857713721</v>
       </c>
       <c r="F21">
-        <v>-0.7195312965616376</v>
+        <v>-0.8919430247518685</v>
       </c>
       <c r="G21">
-        <v>-13.33294853480328</v>
+        <v>-16.22485903790593</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.288002868088315</v>
       </c>
       <c r="E22">
-        <v>-35.96264066373634</v>
+        <v>-39.53646480161271</v>
       </c>
       <c r="F22">
-        <v>-0.8649598433646112</v>
+        <v>-1.177091650385614</v>
       </c>
       <c r="G22">
-        <v>-12.45262150718244</v>
+        <v>-17.84261339494496</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.65190296955363</v>
       </c>
       <c r="E23">
-        <v>-35.91263498950664</v>
+        <v>-39.61952154338739</v>
       </c>
       <c r="F23">
-        <v>-0.6151429048513618</v>
+        <v>-0.5074580292780989</v>
       </c>
       <c r="G23">
-        <v>-11.72474841219058</v>
+        <v>-16.9764124651402</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.083171564363035</v>
       </c>
       <c r="E24">
-        <v>-36.60354879733092</v>
+        <v>-38.66981223873577</v>
       </c>
       <c r="F24">
-        <v>-0.6422662442121355</v>
+        <v>-1.331066666161257</v>
       </c>
       <c r="G24">
-        <v>-12.105143336835</v>
+        <v>-16.66193381272821</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.58426478857013</v>
       </c>
       <c r="E25">
-        <v>-36.1836551019177</v>
+        <v>-40.42458912399702</v>
       </c>
       <c r="F25">
-        <v>-0.640287403670794</v>
+        <v>-1.060258497591815</v>
       </c>
       <c r="G25">
-        <v>-11.98989331497635</v>
+        <v>-18.16769406944647</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.152270796365638</v>
       </c>
       <c r="E26">
-        <v>-37.36636118697497</v>
+        <v>-41.12537953363202</v>
       </c>
       <c r="F26">
-        <v>-0.4864082021030355</v>
+        <v>-1.298375808654756</v>
       </c>
       <c r="G26">
-        <v>-11.6146628413732</v>
+        <v>-16.31728781408961</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.7939766952222092</v>
       </c>
       <c r="E27">
-        <v>-36.39995539865707</v>
+        <v>-39.32932107931685</v>
       </c>
       <c r="F27">
-        <v>-0.677450646682496</v>
+        <v>-0.8283406033348625</v>
       </c>
       <c r="G27">
-        <v>-12.49482434171707</v>
+        <v>-15.79278980793903</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.5059385378542346</v>
       </c>
       <c r="E28">
-        <v>-36.44593752373095</v>
+        <v>-39.23576280631838</v>
       </c>
       <c r="F28">
-        <v>-0.6020963355199717</v>
+        <v>-1.149067974211913</v>
       </c>
       <c r="G28">
-        <v>-11.83482074082581</v>
+        <v>-17.05461913768717</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.281004166720891</v>
       </c>
       <c r="E29">
-        <v>-36.37767757077633</v>
+        <v>-40.83501830873421</v>
       </c>
       <c r="F29">
-        <v>-0.3199860496849966</v>
+        <v>-1.532019150506579</v>
       </c>
       <c r="G29">
-        <v>-11.86770438966739</v>
+        <v>-16.02267905600433</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.118631677951869</v>
       </c>
       <c r="E30">
-        <v>-35.86687249542213</v>
+        <v>-40.2608055403246</v>
       </c>
       <c r="F30">
-        <v>-0.6189548849898245</v>
+        <v>-0.73057685346887</v>
       </c>
       <c r="G30">
-        <v>-11.53435562768156</v>
+        <v>-14.27363011815057</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.01466418945808665</v>
       </c>
       <c r="E31">
-        <v>-36.43000408793497</v>
+        <v>-40.97730749052921</v>
       </c>
       <c r="F31">
-        <v>-0.6518468731475865</v>
+        <v>-1.337404657234845</v>
       </c>
       <c r="G31">
-        <v>-11.78143819400506</v>
+        <v>-16.95930522106601</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.03819469681352941</v>
       </c>
       <c r="E32">
-        <v>-35.55964949755676</v>
+        <v>-37.4896534203078</v>
       </c>
       <c r="F32">
-        <v>-0.6484371543116453</v>
+        <v>-0.9030741017785346</v>
       </c>
       <c r="G32">
-        <v>-11.24988044949199</v>
+        <v>-15.65398856511401</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.04308002942824496</v>
       </c>
       <c r="E33">
-        <v>-35.05784023581879</v>
+        <v>-39.0180405687406</v>
       </c>
       <c r="F33">
-        <v>-0.3243238201873852</v>
+        <v>-1.886801741536282</v>
       </c>
       <c r="G33">
-        <v>-12.47005815053778</v>
+        <v>-17.23233087750802</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.002648883001434933</v>
       </c>
       <c r="E34">
-        <v>-35.40064118972543</v>
+        <v>-39.42782218169469</v>
       </c>
       <c r="F34">
-        <v>-0.5676261844174744</v>
+        <v>-1.341392428729922</v>
       </c>
       <c r="G34">
-        <v>-11.80460870223442</v>
+        <v>-15.85399682914184</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.07809965479330365</v>
       </c>
       <c r="E35">
-        <v>-34.65964698785032</v>
+        <v>-39.68567349169144</v>
       </c>
       <c r="F35">
-        <v>-0.3813657398496832</v>
+        <v>-1.952771011443913</v>
       </c>
       <c r="G35">
-        <v>-12.53166740302362</v>
+        <v>-15.06561358278319</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.1953409996324698</v>
       </c>
       <c r="E36">
-        <v>-34.69632083460144</v>
+        <v>-40.45211771748965</v>
       </c>
       <c r="F36">
-        <v>-0.6177314721701476</v>
+        <v>-1.303387446024164</v>
       </c>
       <c r="G36">
-        <v>-12.3005416661994</v>
+        <v>-16.92546482456358</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.346630099343416</v>
       </c>
       <c r="E37">
-        <v>-34.86928363508741</v>
+        <v>-40.48911535013232</v>
       </c>
       <c r="F37">
-        <v>-0.5583448759000414</v>
+        <v>-2.136393001956582</v>
       </c>
       <c r="G37">
-        <v>-12.19410100602076</v>
+        <v>-16.62447995576966</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.5258543609040074</v>
       </c>
       <c r="E38">
-        <v>-33.82955505987431</v>
+        <v>-40.01503167050631</v>
       </c>
       <c r="F38">
-        <v>-0.6877922463103155</v>
+        <v>-1.302769800717142</v>
       </c>
       <c r="G38">
-        <v>-12.53835470501295</v>
+        <v>-16.98221916201608</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.7252496493166267</v>
       </c>
       <c r="E39">
-        <v>-34.41297421594151</v>
+        <v>-37.20766534385017</v>
       </c>
       <c r="F39">
-        <v>-0.6924332964955109</v>
+        <v>-1.382388240056987</v>
       </c>
       <c r="G39">
-        <v>-12.76774240542905</v>
+        <v>-16.58388604636712</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.9393396198699888</v>
       </c>
       <c r="E40">
-        <v>-32.95646074272145</v>
+        <v>-38.65554980984861</v>
       </c>
       <c r="F40">
-        <v>-0.448607517460369</v>
+        <v>-0.6652386903685424</v>
       </c>
       <c r="G40">
-        <v>-13.03959116293184</v>
+        <v>-17.6661017278821</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.161419079465782</v>
       </c>
       <c r="E41">
-        <v>-32.54172950767698</v>
+        <v>-37.08002351123297</v>
       </c>
       <c r="F41">
-        <v>-0.4285166242171042</v>
+        <v>-1.752193865400549</v>
       </c>
       <c r="G41">
-        <v>-13.26864118770294</v>
+        <v>-18.46440171340365</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.383407456012798</v>
       </c>
       <c r="E42">
-        <v>-31.9107364679222</v>
+        <v>-34.85546726089001</v>
       </c>
       <c r="F42">
-        <v>-0.6768559651112485</v>
+        <v>-1.640849837309663</v>
       </c>
       <c r="G42">
-        <v>-12.61423902986412</v>
+        <v>-18.18874086271238</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.602069199421713</v>
       </c>
       <c r="E43">
-        <v>-31.91135234038725</v>
+        <v>-35.68496143029701</v>
       </c>
       <c r="F43">
-        <v>-0.5085753338014414</v>
+        <v>-0.673054279061236</v>
       </c>
       <c r="G43">
-        <v>-13.25227054001124</v>
+        <v>-15.53844059415682</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.814163245880728</v>
       </c>
       <c r="E44">
-        <v>-30.56364224791249</v>
+        <v>-35.20654626528267</v>
       </c>
       <c r="F44">
-        <v>-0.4365167146489465</v>
+        <v>-0.376552065719705</v>
       </c>
       <c r="G44">
-        <v>-13.17723371481812</v>
+        <v>-17.48917293208129</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.014603181608349</v>
       </c>
       <c r="E45">
-        <v>-29.25921983847705</v>
+        <v>-34.64854769805753</v>
       </c>
       <c r="F45">
-        <v>-0.4908362438426042</v>
+        <v>-1.072108577104091</v>
       </c>
       <c r="G45">
-        <v>-13.33917236041711</v>
+        <v>-17.88100082574558</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.202442014354574</v>
       </c>
       <c r="E46">
-        <v>-30.48899035389604</v>
+        <v>-34.07889283873664</v>
       </c>
       <c r="F46">
-        <v>-0.3826485416411892</v>
+        <v>-1.663835744966351</v>
       </c>
       <c r="G46">
-        <v>-12.70871868900938</v>
+        <v>-17.14016197914917</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.377820920319447</v>
       </c>
       <c r="E47">
-        <v>-29.04912581536519</v>
+        <v>-35.98984547133742</v>
       </c>
       <c r="F47">
-        <v>-0.4285768050418909</v>
+        <v>-0.7190815240816527</v>
       </c>
       <c r="G47">
-        <v>-13.00391341365512</v>
+        <v>-18.36247001624949</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.53935128304844</v>
       </c>
       <c r="E48">
-        <v>-30.66488081282796</v>
+        <v>-33.65290155307209</v>
       </c>
       <c r="F48">
-        <v>-0.5313585271009533</v>
+        <v>-1.176550814815492</v>
       </c>
       <c r="G48">
-        <v>-13.29516858910912</v>
+        <v>-18.5010047601586</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.687555967239317</v>
       </c>
       <c r="E49">
-        <v>-28.7949153984706</v>
+        <v>-35.03348610260554</v>
       </c>
       <c r="F49">
-        <v>-0.3481380060378482</v>
+        <v>-1.310624982057722</v>
       </c>
       <c r="G49">
-        <v>-13.129551927416</v>
+        <v>-17.11146617041477</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.825987196345879</v>
       </c>
       <c r="E50">
-        <v>-28.28795273331191</v>
+        <v>-32.50686252205492</v>
       </c>
       <c r="F50">
-        <v>-0.582372070196131</v>
+        <v>-1.50546752898128</v>
       </c>
       <c r="G50">
-        <v>-13.75725784602613</v>
+        <v>-17.37794191250732</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.955724210146864</v>
       </c>
       <c r="E51">
-        <v>-28.49546099776539</v>
+        <v>-31.72152550269671</v>
       </c>
       <c r="F51">
-        <v>-0.4546493555277705</v>
+        <v>-0.7236687282657231</v>
       </c>
       <c r="G51">
-        <v>-13.63579061964473</v>
+        <v>-17.69433571551378</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.075831437694243</v>
       </c>
       <c r="E52">
-        <v>-26.81287478089741</v>
+        <v>-30.90679415855472</v>
       </c>
       <c r="F52">
-        <v>-0.1117334729224555</v>
+        <v>-0.6206700384962455</v>
       </c>
       <c r="G52">
-        <v>-13.46301324795017</v>
+        <v>-19.37650170183764</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.190114324555877</v>
       </c>
       <c r="E53">
-        <v>-28.24392238053533</v>
+        <v>-32.40974260424942</v>
       </c>
       <c r="F53">
-        <v>-0.3171543835081908</v>
+        <v>-0.8202241105182353</v>
       </c>
       <c r="G53">
-        <v>-14.05642853586453</v>
+        <v>-18.3166123394395</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.299379573808974</v>
       </c>
       <c r="E54">
-        <v>-26.29363089422991</v>
+        <v>-31.45367532209103</v>
       </c>
       <c r="F54">
-        <v>-0.368884553530105</v>
+        <v>-0.6750315358966622</v>
       </c>
       <c r="G54">
-        <v>-14.34015884130776</v>
+        <v>-17.13267186986657</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.399766152750106</v>
       </c>
       <c r="E55">
-        <v>-26.14693097875143</v>
+        <v>-32.72135595766523</v>
       </c>
       <c r="F55">
-        <v>-0.2989544351279607</v>
+        <v>-0.6323585800051463</v>
       </c>
       <c r="G55">
-        <v>-14.30884770159734</v>
+        <v>-18.0739179012283</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.493442598660188</v>
       </c>
       <c r="E56">
-        <v>-26.09894726816616</v>
+        <v>-31.62271646408635</v>
       </c>
       <c r="F56">
-        <v>-0.2377909208207315</v>
+        <v>-0.8931474331005601</v>
       </c>
       <c r="G56">
-        <v>-14.22828061008086</v>
+        <v>-17.95298367267872</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.580129322246819</v>
       </c>
       <c r="E57">
-        <v>-25.85512969911918</v>
+        <v>-30.91133848222142</v>
       </c>
       <c r="F57">
-        <v>0.2373834101947626</v>
+        <v>-0.5349297839402692</v>
       </c>
       <c r="G57">
-        <v>-14.12177208371866</v>
+        <v>-20.37454676301665</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.654825379677403</v>
       </c>
       <c r="E58">
-        <v>-25.48866746852246</v>
+        <v>-29.32573406470171</v>
       </c>
       <c r="F58">
-        <v>-0.3347984511121017</v>
+        <v>-0.9956393369770972</v>
       </c>
       <c r="G58">
-        <v>-14.1679210885361</v>
+        <v>-19.66785288311228</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.71739316165883</v>
       </c>
       <c r="E59">
-        <v>-24.40979929246107</v>
+        <v>-29.96319829381345</v>
       </c>
       <c r="F59">
-        <v>-0.402889095093463</v>
+        <v>-1.150954959810159</v>
       </c>
       <c r="G59">
-        <v>-15.00365506774296</v>
+        <v>-18.09841262767337</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.769098598107799</v>
       </c>
       <c r="E60">
-        <v>-24.62861968498571</v>
+        <v>-29.45721151480341</v>
       </c>
       <c r="F60">
-        <v>-0.6413983733704747</v>
+        <v>-0.4736166094240311</v>
       </c>
       <c r="G60">
-        <v>-14.6093392991059</v>
+        <v>-20.15153351803642</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.80803362364008</v>
       </c>
       <c r="E61">
-        <v>-25.60005887216314</v>
+        <v>-28.29456883383711</v>
       </c>
       <c r="F61">
-        <v>-0.5856091650872893</v>
+        <v>-1.382871270361197</v>
       </c>
       <c r="G61">
-        <v>-15.22880858041433</v>
+        <v>-19.93431869356822</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.833951134716363</v>
       </c>
       <c r="E62">
-        <v>-24.41591726084543</v>
+        <v>-28.89739929373819</v>
       </c>
       <c r="F62">
-        <v>-0.4985655205629064</v>
+        <v>-1.353309815743604</v>
       </c>
       <c r="G62">
-        <v>-14.89947551016763</v>
+        <v>-20.69320828971751</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.852579203063055</v>
       </c>
       <c r="E63">
-        <v>-22.72793310296031</v>
+        <v>-28.25592736512966</v>
       </c>
       <c r="F63">
-        <v>-0.3027695826782543</v>
+        <v>-0.6562852089756055</v>
       </c>
       <c r="G63">
-        <v>-14.5413721439119</v>
+        <v>-21.09104978935388</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.865457187365763</v>
       </c>
       <c r="E64">
-        <v>-23.30249229963151</v>
+        <v>-27.76067986222881</v>
       </c>
       <c r="F64">
-        <v>-0.6693143575419258</v>
+        <v>-0.9486753299076981</v>
       </c>
       <c r="G64">
-        <v>-15.29006857034577</v>
+        <v>-21.83587287750681</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.871238182545795</v>
       </c>
       <c r="E65">
-        <v>-22.9941892607153</v>
+        <v>-28.74476707730966</v>
       </c>
       <c r="F65">
-        <v>-0.4392201006466017</v>
+        <v>-1.22482771408879</v>
       </c>
       <c r="G65">
-        <v>-15.19928679056788</v>
+        <v>-18.59654048333089</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.876631586767099</v>
       </c>
       <c r="E66">
-        <v>-23.2880872238131</v>
+        <v>-30.71319963048981</v>
       </c>
       <c r="F66">
-        <v>-0.298515748589384</v>
+        <v>-1.655392216878186</v>
       </c>
       <c r="G66">
-        <v>-14.61575844690655</v>
+        <v>-18.96002514136071</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.883755766432062</v>
       </c>
       <c r="E67">
-        <v>-22.95411679422142</v>
+        <v>-27.77156178526924</v>
       </c>
       <c r="F67">
-        <v>-0.6037402222601977</v>
+        <v>-0.981781910217002</v>
       </c>
       <c r="G67">
-        <v>-15.43457057258942</v>
+        <v>-21.09776192043476</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.888936564780129</v>
       </c>
       <c r="E68">
-        <v>-23.3125273980325</v>
+        <v>-30.42411317102515</v>
       </c>
       <c r="F68">
-        <v>-0.9353888291301188</v>
+        <v>-1.592279160589051</v>
       </c>
       <c r="G68">
-        <v>-14.60720565250584</v>
+        <v>-19.03034609443313</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.896598300028449</v>
       </c>
       <c r="E69">
-        <v>-23.72919681995226</v>
+        <v>-27.37346816372895</v>
       </c>
       <c r="F69">
-        <v>-0.8198875730112045</v>
+        <v>-1.733516429686814</v>
       </c>
       <c r="G69">
-        <v>-14.70372626297607</v>
+        <v>-18.08300203818806</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.908360839675508</v>
       </c>
       <c r="E70">
-        <v>-23.23952839702886</v>
+        <v>-29.08552568943884</v>
       </c>
       <c r="F70">
-        <v>-0.7112390123883966</v>
+        <v>-1.159520433253813</v>
       </c>
       <c r="G70">
-        <v>-14.90160750149492</v>
+        <v>-19.51827415928416</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.920258965049031</v>
       </c>
       <c r="E71">
-        <v>-23.25660527251178</v>
+        <v>-30.72440760365879</v>
       </c>
       <c r="F71">
-        <v>-0.8846959864828176</v>
+        <v>-1.983493322497522</v>
       </c>
       <c r="G71">
-        <v>-14.98702288695366</v>
+        <v>-18.65987121949714</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.933024864222845</v>
       </c>
       <c r="E72">
-        <v>-23.66530910865205</v>
+        <v>-28.58788262378793</v>
       </c>
       <c r="F72">
-        <v>-0.8832278910992052</v>
+        <v>-2.01718904140737</v>
       </c>
       <c r="G72">
-        <v>-14.19908821951557</v>
+        <v>-19.57385159779744</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.949033853597526</v>
       </c>
       <c r="E73">
-        <v>-23.20661544794111</v>
+        <v>-28.83342554143183</v>
       </c>
       <c r="F73">
-        <v>-1.318366928425348</v>
+        <v>-1.779747972770322</v>
       </c>
       <c r="G73">
-        <v>-14.63074363129006</v>
+        <v>-18.39117410134774</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.965457377721481</v>
       </c>
       <c r="E74">
-        <v>-23.91239623593257</v>
+        <v>-27.18058687032024</v>
       </c>
       <c r="F74">
-        <v>-1.472184365462404</v>
+        <v>-2.552872816187016</v>
       </c>
       <c r="G74">
-        <v>-14.01462958788569</v>
+        <v>-18.92132486400662</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.979469690484033</v>
       </c>
       <c r="E75">
-        <v>-23.97949916377822</v>
+        <v>-29.74475602886845</v>
       </c>
       <c r="F75">
-        <v>-1.260944127490387</v>
+        <v>-1.699142884645158</v>
       </c>
       <c r="G75">
-        <v>-14.38270597257848</v>
+        <v>-18.80364821226769</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.994966954813624</v>
       </c>
       <c r="E76">
-        <v>-23.32442822772466</v>
+        <v>-27.11677161460415</v>
       </c>
       <c r="F76">
-        <v>-1.275230738553566</v>
+        <v>-1.848087258580407</v>
       </c>
       <c r="G76">
-        <v>-13.63587007273767</v>
+        <v>-18.81298560596121</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.010049166825264</v>
       </c>
       <c r="E77">
-        <v>-23.81132522455537</v>
+        <v>-28.4876131523101</v>
       </c>
       <c r="F77">
-        <v>-1.445243152281906</v>
+        <v>-2.646888726004121</v>
       </c>
       <c r="G77">
-        <v>-14.11845657236108</v>
+        <v>-18.19133798568794</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.019457496977584</v>
       </c>
       <c r="E78">
-        <v>-25.01751144734241</v>
+        <v>-28.60406738989134</v>
       </c>
       <c r="F78">
-        <v>-1.60596158784549</v>
+        <v>-2.593806071130422</v>
       </c>
       <c r="G78">
-        <v>-13.11648189362696</v>
+        <v>-18.53873504766967</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.027313007843549</v>
       </c>
       <c r="E79">
-        <v>-24.80273951058063</v>
+        <v>-31.61474182135884</v>
       </c>
       <c r="F79">
-        <v>-1.672120902462973</v>
+        <v>-2.699664933783184</v>
       </c>
       <c r="G79">
-        <v>-13.08171454437353</v>
+        <v>-16.58225229214349</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.033810321890038</v>
       </c>
       <c r="E80">
-        <v>-25.26432233770846</v>
+        <v>-28.35604286849124</v>
       </c>
       <c r="F80">
-        <v>-1.623589818390246</v>
+        <v>-1.681370536862097</v>
       </c>
       <c r="G80">
-        <v>-13.02855711464945</v>
+        <v>-16.78631762972971</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.034076588403587</v>
       </c>
       <c r="E81">
-        <v>-25.20249961055575</v>
+        <v>-30.91631074668184</v>
       </c>
       <c r="F81">
-        <v>-1.251274811023671</v>
+        <v>-2.519624494198281</v>
       </c>
       <c r="G81">
-        <v>-12.87753995878452</v>
+        <v>-16.55635720493531</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.031316705186021</v>
       </c>
       <c r="E82">
-        <v>-25.78534138618697</v>
+        <v>-30.20706567607451</v>
       </c>
       <c r="F82">
-        <v>-1.965309211176447</v>
+        <v>-2.381481786459287</v>
       </c>
       <c r="G82">
-        <v>-12.56634536754749</v>
+        <v>-15.89306954286909</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.02610652972148</v>
       </c>
       <c r="E83">
-        <v>-26.17503015996903</v>
+        <v>-31.55856610129369</v>
       </c>
       <c r="F83">
-        <v>-1.872378931764375</v>
+        <v>-2.450856815938069</v>
       </c>
       <c r="G83">
-        <v>-12.53296844742055</v>
+        <v>-16.7650523404582</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.013762449652277</v>
       </c>
       <c r="E84">
-        <v>-27.83168633466908</v>
+        <v>-31.38599048533538</v>
       </c>
       <c r="F84">
-        <v>-1.792506307625102</v>
+        <v>-2.424456438327693</v>
       </c>
       <c r="G84">
-        <v>-12.3136249421706</v>
+        <v>-14.47726674008945</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.992683428892369</v>
       </c>
       <c r="E85">
-        <v>-27.96298943852148</v>
+        <v>-33.5402648190793</v>
       </c>
       <c r="F85">
-        <v>-2.034909126895222</v>
+        <v>-2.453793798558252</v>
       </c>
       <c r="G85">
-        <v>-12.71775647833159</v>
+        <v>-15.92552944188165</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.962736832850089</v>
       </c>
       <c r="E86">
-        <v>-28.20853688463939</v>
+        <v>-34.42147869012791</v>
       </c>
       <c r="F86">
-        <v>-1.796125075641881</v>
+        <v>-1.564052770058173</v>
       </c>
       <c r="G86">
-        <v>-12.291023847774</v>
+        <v>-14.4974561020607</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.91884431328463</v>
       </c>
       <c r="E87">
-        <v>-29.47204453141553</v>
+        <v>-34.9410101348949</v>
       </c>
       <c r="F87">
-        <v>-1.921819854885522</v>
+        <v>-2.921003672525001</v>
       </c>
       <c r="G87">
-        <v>-12.36528931585647</v>
+        <v>-14.71820658916484</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.855962629773228</v>
       </c>
       <c r="E88">
-        <v>-30.74969233828062</v>
+        <v>-33.33878848200405</v>
       </c>
       <c r="F88">
-        <v>-2.140111543446033</v>
+        <v>-2.954689097346398</v>
       </c>
       <c r="G88">
-        <v>-11.78585777229999</v>
+        <v>-13.64483171951248</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.775981995654088</v>
       </c>
       <c r="E89">
-        <v>-31.90338675460776</v>
+        <v>-36.11863074364156</v>
       </c>
       <c r="F89">
-        <v>-2.119156738625896</v>
+        <v>-2.886150264590967</v>
       </c>
       <c r="G89">
-        <v>-11.72950566613052</v>
+        <v>-13.64265669109318</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.676280182704102</v>
       </c>
       <c r="E90">
-        <v>-33.7110584805156</v>
+        <v>-37.16344932363928</v>
       </c>
       <c r="F90">
-        <v>-2.245068485579952</v>
+        <v>-2.477026764337748</v>
       </c>
       <c r="G90">
-        <v>-11.60889256049825</v>
+        <v>-15.6818236320082</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.552318529578726</v>
       </c>
       <c r="E91">
-        <v>-34.24057068199549</v>
+        <v>-37.59409814482071</v>
       </c>
       <c r="F91">
-        <v>-2.213648552070591</v>
+        <v>-3.007250712973918</v>
       </c>
       <c r="G91">
-        <v>-11.19436922188949</v>
+        <v>-14.31393932063674</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.405060028531336</v>
       </c>
       <c r="E92">
-        <v>-36.02589212443848</v>
+        <v>-38.44707471619449</v>
       </c>
       <c r="F92">
-        <v>-2.670938092183027</v>
+        <v>-2.822431440789176</v>
       </c>
       <c r="G92">
-        <v>-11.66565186376905</v>
+        <v>-14.47879952267413</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.23149530872113</v>
       </c>
       <c r="E93">
-        <v>-37.02712867058638</v>
+        <v>-41.57733256078254</v>
       </c>
       <c r="F93">
-        <v>-2.733248209573035</v>
+        <v>-3.236854021035455</v>
       </c>
       <c r="G93">
-        <v>-11.37595595526405</v>
+        <v>-14.73090418658071</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.026059462447127</v>
       </c>
       <c r="E94">
-        <v>-37.75128147762695</v>
+        <v>-41.10425420238624</v>
       </c>
       <c r="F94">
-        <v>-2.850315750842319</v>
+        <v>-3.729517216475147</v>
       </c>
       <c r="G94">
-        <v>-11.0835420888713</v>
+        <v>-15.11384988656314</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.786906839404714</v>
       </c>
       <c r="E95">
-        <v>-39.74868267903416</v>
+        <v>-42.36094196730683</v>
       </c>
       <c r="F95">
-        <v>-2.644702419987857</v>
+        <v>-2.992375755163152</v>
       </c>
       <c r="G95">
-        <v>-11.25447879724603</v>
+        <v>-16.45197239353655</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.509797435105865</v>
       </c>
       <c r="E96">
-        <v>-41.27718530355415</v>
+        <v>-45.4520692679946</v>
       </c>
       <c r="F96">
-        <v>-2.696095260649783</v>
+        <v>-3.646532610212036</v>
       </c>
       <c r="G96">
-        <v>-11.53682529465386</v>
+        <v>-13.78978726649501</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.194882439875526</v>
       </c>
       <c r="E97">
-        <v>-41.98852479339002</v>
+        <v>-46.22265931174682</v>
       </c>
       <c r="F97">
-        <v>-2.932848209066572</v>
+        <v>-4.053122972853509</v>
       </c>
       <c r="G97">
-        <v>-11.20073871150704</v>
+        <v>-13.7245347586432</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.837443345075476</v>
       </c>
       <c r="E98">
-        <v>-44.86825613468873</v>
+        <v>-48.67141578173555</v>
       </c>
       <c r="F98">
-        <v>-3.314418393802975</v>
+        <v>-3.264818308237327</v>
       </c>
       <c r="G98">
-        <v>-12.10441170627082</v>
+        <v>-15.44231724915132</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.452018739193393</v>
       </c>
       <c r="E99">
-        <v>-46.31184760732789</v>
+        <v>-50.22795871731103</v>
       </c>
       <c r="F99">
-        <v>-3.300645695309356</v>
+        <v>-3.182662772020948</v>
       </c>
       <c r="G99">
-        <v>-11.88338975443246</v>
+        <v>-14.29970397481787</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.032161712954229</v>
       </c>
       <c r="E100">
-        <v>-48.26248099342089</v>
+        <v>-51.34948285428767</v>
       </c>
       <c r="F100">
-        <v>-3.29462998838956</v>
+        <v>-3.934871611412434</v>
       </c>
       <c r="G100">
-        <v>-12.44216680436942</v>
+        <v>-16.54255223003655</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.6083144194941467</v>
       </c>
       <c r="E101">
-        <v>-50.31548393081277</v>
+        <v>-52.606609881187</v>
       </c>
       <c r="F101">
-        <v>-3.267538323147094</v>
+        <v>-4.079562151258813</v>
       </c>
       <c r="G101">
-        <v>-11.93953991732404</v>
+        <v>-14.47603687242161</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.1592309498320844</v>
       </c>
       <c r="E102">
-        <v>-51.79856935739134</v>
+        <v>-52.50091756208498</v>
       </c>
       <c r="F102">
-        <v>-3.558682859376694</v>
+        <v>-4.180643765017651</v>
       </c>
       <c r="G102">
-        <v>-11.8983567308155</v>
+        <v>-15.01348242217628</v>
       </c>
     </row>
   </sheetData>
